--- a/reparto_superficie_adicional_territorio.xlsx
+++ b/reparto_superficie_adicional_territorio.xlsx
@@ -581,7 +581,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Externas (viñedo, frutales, hortícolas): potencial SIGPAC − superficie declarada, repartido por proporción del potencial SIGPAC de cada territorio (agregado, no por titular). ABRS sin derecho: Σ(SUP_Det_Ctr_ABRS − DERECHOS)≥0 sobre la base &gt;300, atribuida titular-a-titular por TH; ya está incluida en SUP_Det_Ctr_ABRS, por lo que NO se suma al denominador del modelo (es activación de superficie ya existente).</t>
+          <t>Externas (viñedo, frutales, hortícolas): potencial SIGPAC − superficie declarada, repartido por proporción del potencial SIGPAC de cada territorio (agregado, no por titular). ABRS sin derecho: Σ(SUP_Det_Ctr_ABRS − DERECHOS)≥0 sobre la base &gt;300, atribuida titular-a-titular por TH; en el modelo de pago por superficie activable min(derechos, ABRS) NO genera pago por defecto y solo se suma al denominador si se reactiva con el Filtro B (repartida titular a titular según su exceso).</t>
         </is>
       </c>
     </row>
